--- a/combined_capacity_and_relaxation_end_potentials.xlsx
+++ b/combined_capacity_and_relaxation_end_potentials.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,1506 +442,2026 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13.9840932393779</v>
+        <v>13.6045938682195</v>
       </c>
       <c r="B2" t="n">
-        <v>2.22192502021789</v>
+        <v>2.40348291397094</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>27.7347143737287</v>
+        <v>27.7905667406479</v>
       </c>
       <c r="B3" t="n">
-        <v>2.21881341934204</v>
+        <v>2.39621114730835</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>41.9517193399875</v>
+        <v>41.5115166554937</v>
       </c>
       <c r="B4" t="n">
-        <v>2.21688532829284</v>
+        <v>2.39149689674377</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55.7028494913118</v>
+        <v>55.6974672376893</v>
       </c>
       <c r="B5" t="n">
-        <v>2.21474742889404</v>
+        <v>2.38855767250061</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69.9208998396582</v>
+        <v>69.418299092448</v>
       </c>
       <c r="B6" t="n">
-        <v>2.21194124221801</v>
+        <v>2.38592386245727</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83.6722887026865</v>
+        <v>83.6043764541665</v>
       </c>
       <c r="B7" t="n">
-        <v>2.20903944969177</v>
+        <v>2.38370990753173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97.890292359478</v>
+        <v>97.32517769139049</v>
       </c>
       <c r="B8" t="n">
-        <v>2.20651960372924</v>
+        <v>2.38195395469665</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111.641315520396</v>
+        <v>111.511087140188</v>
       </c>
       <c r="B9" t="n">
-        <v>2.20497345924377</v>
+        <v>2.37983560562133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125.858343013121</v>
+        <v>125.23186963094</v>
       </c>
       <c r="B10" t="n">
-        <v>2.20382809638977</v>
+        <v>2.37714433670043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>139.609573658741</v>
+        <v>139.418035546311</v>
       </c>
       <c r="B11" t="n">
-        <v>2.20251083374023</v>
+        <v>2.37361359596252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>153.826619299995</v>
+        <v>153.138864905701</v>
       </c>
       <c r="B12" t="n">
-        <v>2.20062088966369</v>
+        <v>2.36588382720947</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>167.577108647908</v>
+        <v>167.324793029094</v>
       </c>
       <c r="B13" t="n">
-        <v>2.19640207290649</v>
+        <v>2.35303902626037</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>181.794560075164</v>
+        <v>181.045589340769</v>
       </c>
       <c r="B14" t="n">
-        <v>2.18956804275512</v>
+        <v>2.33305597305297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>195.545603528904</v>
+        <v>195.231481250966</v>
       </c>
       <c r="B15" t="n">
-        <v>2.18164587020874</v>
+        <v>2.30186963081359</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>209.762010655731</v>
+        <v>208.952198577518</v>
       </c>
       <c r="B16" t="n">
-        <v>2.17200565338134</v>
+        <v>2.26163673400878</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>223.512996873202</v>
+        <v>223.138078702671</v>
       </c>
       <c r="B17" t="n">
-        <v>2.16847395896911</v>
+        <v>2.22336959838867</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>237.729940060053</v>
+        <v>236.858780052116</v>
       </c>
       <c r="B18" t="n">
-        <v>2.16639328002929</v>
+        <v>2.19157242774963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>251.480528770089</v>
+        <v>251.04459917623</v>
       </c>
       <c r="B19" t="n">
-        <v>2.16578245162963</v>
+        <v>2.16458487510681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>265.697594451553</v>
+        <v>264.765343649783</v>
       </c>
       <c r="B20" t="n">
-        <v>2.16933298110961</v>
+        <v>2.1405177116394</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>279.448309323615</v>
+        <v>278.951196502724</v>
       </c>
       <c r="B21" t="n">
-        <v>2.17471623420715</v>
+        <v>2.11753821372985</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>293.66442381927</v>
+        <v>292.671971305983</v>
       </c>
       <c r="B22" t="n">
-        <v>2.18069148063659</v>
+        <v>2.12585973739624</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>307.41481652188</v>
+        <v>306.858063721258</v>
       </c>
       <c r="B23" t="n">
-        <v>2.18617010116577</v>
+        <v>2.13708233833313</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>321.630470762491</v>
+        <v>320.578873874782</v>
       </c>
       <c r="B24" t="n">
-        <v>2.19044613838195</v>
+        <v>2.14089941978454</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>335.380959070831</v>
+        <v>334.764779276041</v>
       </c>
       <c r="B25" t="n">
-        <v>2.19359588623046</v>
+        <v>2.14296078681945</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>349.598122306576</v>
+        <v>348.485805829742</v>
       </c>
       <c r="B26" t="n">
-        <v>2.19584846496582</v>
+        <v>2.1446783542633</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>363.350400083903</v>
+        <v>362.671724073766</v>
       </c>
       <c r="B27" t="n">
-        <v>2.19768118858337</v>
+        <v>2.14544177055358</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>377.568437662215</v>
+        <v>376.392540322449</v>
       </c>
       <c r="B28" t="n">
-        <v>2.19909381866455</v>
+        <v>2.14614796638488</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>391.319482819484</v>
+        <v>390.5784391961</v>
       </c>
       <c r="B29" t="n">
-        <v>2.20025825500488</v>
+        <v>2.14664435386657</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>405.536463435147</v>
+        <v>404.299538735059</v>
       </c>
       <c r="B30" t="n">
-        <v>2.20109820365905</v>
+        <v>2.14752221107482</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>419.287383272478</v>
+        <v>418.485483072797</v>
       </c>
       <c r="B31" t="n">
-        <v>2.20146083831787</v>
+        <v>2.14746499061584</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>433.503952466773</v>
+        <v>432.206274342969</v>
       </c>
       <c r="B32" t="n">
-        <v>2.2019190788269</v>
+        <v>2.14738869667053</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>447.254681100674</v>
+        <v>446.392197411467</v>
       </c>
       <c r="B33" t="n">
-        <v>2.20226263999939</v>
+        <v>2.14727401733398</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>461.471000032509</v>
+        <v>460.113227646581</v>
       </c>
       <c r="B34" t="n">
-        <v>2.20239639282226</v>
+        <v>2.14763665199279</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>475.222219023156</v>
+        <v>474.299167446783</v>
       </c>
       <c r="B35" t="n">
-        <v>2.20243453979492</v>
+        <v>2.14691138267517</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>489.438825815849</v>
+        <v>488.019986682192</v>
       </c>
       <c r="B36" t="n">
-        <v>2.2027781009674</v>
+        <v>2.14633893966674</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>503.189361890198</v>
+        <v>502.205887867706</v>
       </c>
       <c r="B37" t="n">
-        <v>2.20270180702209</v>
+        <v>2.14588093757629</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>517.406226572063</v>
+        <v>515.926705306335</v>
       </c>
       <c r="B38" t="n">
-        <v>2.20285439491272</v>
+        <v>2.14513635635376</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>531.157079456621</v>
+        <v>530.1125617653259</v>
       </c>
       <c r="B39" t="n">
-        <v>2.20264458656311</v>
+        <v>2.14433479309082</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>545.373358559402</v>
+        <v>543.833355604011</v>
       </c>
       <c r="B40" t="n">
-        <v>2.20293092727661</v>
+        <v>2.1435523033142</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>559.123767402854</v>
+        <v>558.019359584392</v>
       </c>
       <c r="B41" t="n">
-        <v>2.20283532142639</v>
+        <v>2.14303708076477</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>573.340582110685</v>
+        <v>571.740161760213</v>
       </c>
       <c r="B42" t="n">
-        <v>2.2027781009674</v>
+        <v>2.14185380935668</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>587.091355818612</v>
+        <v>585.926300962307</v>
       </c>
       <c r="B43" t="n">
-        <v>2.20260620117187</v>
+        <v>2.14137649536132</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>601.308240826073</v>
+        <v>599.64708000106</v>
       </c>
       <c r="B44" t="n">
-        <v>2.2027781009674</v>
+        <v>2.14053678512573</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>615.058870049259</v>
+        <v>613.832940543815</v>
       </c>
       <c r="B45" t="n">
-        <v>2.2027781009674</v>
+        <v>2.14002156257629</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>629.276013955106</v>
+        <v>627.553665287874</v>
       </c>
       <c r="B46" t="n">
-        <v>2.20272088050842</v>
+        <v>2.13971614837646</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>643.027191788065</v>
+        <v>641.739734093787</v>
       </c>
       <c r="B47" t="n">
-        <v>2.20258712768554</v>
+        <v>2.13963985443115</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>657.245165981008</v>
+        <v>655.4605337022419</v>
       </c>
       <c r="B48" t="n">
-        <v>2.20283532142639</v>
+        <v>2.1391053199768</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>670.996145269959</v>
+        <v>669.646649573661</v>
       </c>
       <c r="B49" t="n">
-        <v>2.20283532142639</v>
+        <v>2.13914346694946</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>685.212757643532</v>
+        <v>683.367552363265</v>
       </c>
       <c r="B50" t="n">
-        <v>2.20270180702209</v>
+        <v>2.13874268531799</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>698.964222692939</v>
+        <v>697.553500293051</v>
       </c>
       <c r="B51" t="n">
-        <v>2.20279717445373</v>
+        <v>2.13845634460449</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>713.181041849197</v>
+        <v>711.274347484342</v>
       </c>
       <c r="B52" t="n">
-        <v>2.20279717445373</v>
+        <v>2.13824653625488</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>726.932592197637</v>
+        <v>725.460245454002</v>
       </c>
       <c r="B53" t="n">
-        <v>2.20270180702209</v>
+        <v>2.13780760765075</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>741.14947354582</v>
+        <v>739.180953080725</v>
       </c>
       <c r="B54" t="n">
-        <v>2.20281624794006</v>
+        <v>2.1374831199646</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>754.899967906622</v>
+        <v>753.366749611747</v>
       </c>
       <c r="B55" t="n">
-        <v>2.2024917602539</v>
+        <v>2.13719677925109</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>769.116886399281</v>
+        <v>767.087447738214</v>
       </c>
       <c r="B56" t="n">
-        <v>2.2023389339447</v>
+        <v>2.13673877716064</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>782.867942024219</v>
+        <v>781.273255932172</v>
       </c>
       <c r="B57" t="n">
-        <v>2.2023582458496</v>
+        <v>2.13637614250183</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>797.085325169715</v>
+        <v>794.994039086814</v>
       </c>
       <c r="B58" t="n">
-        <v>2.20214819908142</v>
+        <v>2.13597536087036</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>810.836836756344</v>
+        <v>809.179889838835</v>
       </c>
       <c r="B59" t="n">
-        <v>2.20195722579956</v>
+        <v>2.13557434082031</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>825.053361018535</v>
+        <v>822.900611475587</v>
       </c>
       <c r="B60" t="n">
-        <v>2.2017855644226</v>
+        <v>2.13528823852539</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>838.804230637499</v>
+        <v>837.086422453991</v>
       </c>
       <c r="B61" t="n">
-        <v>2.2014992237091</v>
+        <v>2.13488745689392</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>853.020942522311</v>
+        <v>850.807120686991</v>
       </c>
       <c r="B62" t="n">
-        <v>2.20123195648193</v>
+        <v>2.1343719959259</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>866.7722489383031</v>
+        <v>864.992933821896</v>
       </c>
       <c r="B63" t="n">
-        <v>2.20090723037719</v>
+        <v>2.13370394706726</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>880.989624144884</v>
+        <v>878.71356802498</v>
       </c>
       <c r="B64" t="n">
-        <v>2.20041108131408</v>
+        <v>2.13297867774963</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>894.742044829801</v>
+        <v>892.899922297185</v>
       </c>
       <c r="B65" t="n">
-        <v>2.19976186752319</v>
+        <v>2.13198637962341</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>908.958617077439</v>
+        <v>906.620593552787</v>
       </c>
       <c r="B66" t="n">
-        <v>2.19911289215087</v>
+        <v>2.13099384307861</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>922.710994409048</v>
+        <v>920.806411098333</v>
       </c>
       <c r="B67" t="n">
-        <v>2.19792938232421</v>
+        <v>2.12990593910217</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>936.92812027605</v>
+        <v>934.527054819418</v>
       </c>
       <c r="B68" t="n">
-        <v>2.19645953178405</v>
+        <v>2.12860798835754</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>950.679196801038</v>
+        <v>948.713105858996</v>
       </c>
       <c r="B69" t="n">
-        <v>2.19439768791198</v>
+        <v>2.12771105766296</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>964.895628686498</v>
+        <v>962.433901066117</v>
       </c>
       <c r="B70" t="n">
-        <v>2.19170618057251</v>
+        <v>2.12641310691833</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>978.646704902532</v>
+        <v>976.619735644957</v>
       </c>
       <c r="B71" t="n">
-        <v>2.18771648406982</v>
+        <v>2.12488627433776</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>992.862701368301</v>
+        <v>990.340559478063</v>
       </c>
       <c r="B72" t="n">
-        <v>2.18279123306274</v>
+        <v>2.12362670898437</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1006.61372920685</v>
+        <v>1004.52639948631</v>
       </c>
       <c r="B73" t="n">
-        <v>2.17704534530639</v>
+        <v>2.12229061126709</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1020.8302313892</v>
+        <v>1018.24718004334</v>
       </c>
       <c r="B74" t="n">
-        <v>2.16948580741882</v>
+        <v>2.12066841125488</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1034.58117094851</v>
+        <v>1032.43302225408</v>
       </c>
       <c r="B75" t="n">
-        <v>2.15965461730957</v>
+        <v>2.11881709098815</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1048.79742304904</v>
+        <v>1046.15371557926</v>
       </c>
       <c r="B76" t="n">
-        <v>2.14669275283813</v>
+        <v>2.1170802116394</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1062.54923086931</v>
+        <v>1060.33957558114</v>
       </c>
       <c r="B77" t="n">
-        <v>2.12977933883667</v>
+        <v>2.11576318740844</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1076.76526162825</v>
+        <v>1074.06027314203</v>
       </c>
       <c r="B78" t="n">
-        <v>2.10918164253234</v>
+        <v>2.11396932601928</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1090.51664164579</v>
+        <v>1088.24612934784</v>
       </c>
       <c r="B79" t="n">
-        <v>2.08554863929748</v>
+        <v>2.11141180992126</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1104.73348840612</v>
+        <v>1101.96686357259</v>
       </c>
       <c r="B80" t="n">
-        <v>2.0580403804779</v>
+        <v>2.10862517356872</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1118.48491375446</v>
+        <v>1116.15271535212</v>
       </c>
       <c r="B81" t="n">
-        <v>2.02757334709167</v>
+        <v>2.10490345954895</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1132.70076372078</v>
+        <v>1129.87335936694</v>
       </c>
       <c r="B82" t="n">
-        <v>1.98847758769989</v>
+        <v>2.10081911087036</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1146.45163791993</v>
+        <v>1144.05915949035</v>
       </c>
       <c r="B83" t="n">
-        <v>1.94344508647918</v>
+        <v>2.09579944610595</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1160.66808879246</v>
+        <v>1157.77997291645</v>
       </c>
       <c r="B84" t="n">
-        <v>1.88791334629058</v>
+        <v>2.09140968322753</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1174.4192164988</v>
+        <v>1171.96577776382</v>
       </c>
       <c r="B85" t="n">
-        <v>1.82270300388336</v>
+        <v>2.08472967147827</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1188.635993271</v>
+        <v>1185.68650328644</v>
       </c>
       <c r="B86" t="n">
-        <v>1.75550746917724</v>
+        <v>2.07879400253295</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1200.87273690344</v>
+        <v>1199.87232021648</v>
       </c>
       <c r="B87" t="n">
-        <v>1.71326208114624</v>
+        <v>2.07253384590148</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1209.16631566113</v>
+        <v>1213.59307642596</v>
       </c>
       <c r="B88" t="n">
-        <v>1.675426363945</v>
+        <v>2.06631183624267</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1215.92490352341</v>
+        <v>1227.77887947937</v>
       </c>
       <c r="B89" t="n">
-        <v>1.64169490337371</v>
+        <v>2.06012797355651</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1221.99202570896</v>
+        <v>1241.4996339447</v>
       </c>
       <c r="B90" t="n">
-        <v>1.61399590969085</v>
+        <v>2.05543279647827</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1227.12626140066</v>
+        <v>1255.68552930718</v>
       </c>
       <c r="B91" t="n">
-        <v>1.58979022502899</v>
+        <v>2.04676795005798</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1231.81123727611</v>
+        <v>1269.40626594929</v>
       </c>
       <c r="B92" t="n">
-        <v>1.56800889968872</v>
+        <v>2.03982067108154</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1236.32263959632</v>
+        <v>1283.59222936688</v>
       </c>
       <c r="B93" t="n">
-        <v>1.54914832115173</v>
+        <v>2.03212904930114</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1240.28443158287</v>
+        <v>1297.31299048329</v>
       </c>
       <c r="B94" t="n">
-        <v>1.53380024433136</v>
+        <v>2.02134537696838</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1243.97583650442</v>
+        <v>1311.49883152232</v>
       </c>
       <c r="B95" t="n">
-        <v>1.520112991333</v>
+        <v>2.0084433555603</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1247.35520476817</v>
+        <v>1325.21106094587</v>
       </c>
       <c r="B96" t="n">
-        <v>1.5083155632019</v>
+        <v>1.9941861629486</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1250.68059907779</v>
+        <v>1333.69965078109</v>
       </c>
       <c r="B97" t="n">
-        <v>1.49775898456573</v>
+        <v>1.9911515712738</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1253.59396182091</v>
+        <v>1340.53745992314</v>
       </c>
       <c r="B98" t="n">
-        <v>1.4897985458374</v>
+        <v>1.98899483680725</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>13.9218818750592</v>
+        <v>1345.42129202824</v>
       </c>
       <c r="B99" t="n">
-        <v>2.09219169616699</v>
+        <v>1.98588383197784</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>27.6132629619746</v>
+        <v>1349.08993758143</v>
       </c>
       <c r="B100" t="n">
-        <v>2.19111442565918</v>
+        <v>1.98517763614654</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>41.7673078318881</v>
+        <v>1351.42535549756</v>
       </c>
       <c r="B101" t="n">
-        <v>2.21432733535766</v>
+        <v>1.98826956748962</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>55.4586816893895</v>
+        <v>1352.93701894156</v>
       </c>
       <c r="B102" t="n">
-        <v>2.22295594215393</v>
+        <v>1.99512135982513</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>69.61261027422459</v>
+        <v>1354.16339168461</v>
       </c>
       <c r="B103" t="n">
-        <v>2.22837734222412</v>
+        <v>2.00367188453674</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>83.3037950104473</v>
+        <v>1355.11589547408</v>
       </c>
       <c r="B104" t="n">
-        <v>2.231947183609</v>
+        <v>2.01226067543029</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>97.45751725795949</v>
+        <v>1355.81359780268</v>
       </c>
       <c r="B105" t="n">
-        <v>2.23471498489379</v>
+        <v>2.0191695690155</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>111.147628311811</v>
+        <v>2.38422536849975</v>
       </c>
       <c r="B106" t="n">
-        <v>2.23683404922485</v>
+        <v>27.8872908197837</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125.300745915334</v>
+        <v>2.34425950050354</v>
       </c>
       <c r="B107" t="n">
-        <v>2.2382276058197</v>
+        <v>41.8314823778621</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>138.99085556516</v>
+        <v>2.31773018836975</v>
       </c>
       <c r="B108" t="n">
-        <v>2.23931574821472</v>
+        <v>55.7757127597642</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>153.14357178785</v>
+        <v>2.30122089385986</v>
       </c>
       <c r="B109" t="n">
-        <v>2.24015569686889</v>
+        <v>69.7199987483633</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>166.8340560482</v>
+        <v>2.29148697853088</v>
       </c>
       <c r="B110" t="n">
-        <v>2.24097657203674</v>
+        <v>83.6642978661431</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>180.987422406575</v>
+        <v>2.28629565238952</v>
       </c>
       <c r="B111" t="n">
-        <v>2.24175930023193</v>
+        <v>97.6086079783655</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>194.677903737647</v>
+        <v>2.28413891792297</v>
       </c>
       <c r="B112" t="n">
-        <v>2.24237012863159</v>
+        <v>111.552750503914</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>208.831072653023</v>
+        <v>2.28358554840087</v>
       </c>
       <c r="B113" t="n">
-        <v>2.24292373657226</v>
+        <v>125.496933017833</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>222.522105309947</v>
+        <v>2.28268837928772</v>
       </c>
       <c r="B114" t="n">
-        <v>2.24332451820373</v>
+        <v>139.441112732333</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>236.675772151729</v>
+        <v>2.28671550750732</v>
       </c>
       <c r="B115" t="n">
-        <v>2.24403095245361</v>
+        <v>153.385357273157</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>250.366005923464</v>
+        <v>2.28952121734619</v>
       </c>
       <c r="B116" t="n">
-        <v>2.24424076080322</v>
+        <v>167.329611990823</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>264.519416064172</v>
+        <v>2.29249858856201</v>
       </c>
       <c r="B117" t="n">
-        <v>2.24488997459411</v>
+        <v>181.273897212077</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>278.209507719801</v>
+        <v>2.29490327835083</v>
       </c>
       <c r="B118" t="n">
-        <v>2.2452335357666</v>
+        <v>195.218144263387</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>292.362319433219</v>
+        <v>2.29747986793518</v>
       </c>
       <c r="B119" t="n">
-        <v>2.24557709693908</v>
+        <v>209.162421541758</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>306.052838745873</v>
+        <v>2.29921674728393</v>
       </c>
       <c r="B120" t="n">
-        <v>2.24607348442077</v>
+        <v>223.106632967552</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>320.206112119042</v>
+        <v>2.30101084709167</v>
       </c>
       <c r="B121" t="n">
-        <v>2.24634075164794</v>
+        <v>237.050843701093</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>333.896740273349</v>
+        <v>2.30232787132263</v>
       </c>
       <c r="B122" t="n">
-        <v>2.24660801887512</v>
+        <v>250.995039245634</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>348.049658082523</v>
+        <v>2.30488538742065</v>
       </c>
       <c r="B123" t="n">
-        <v>2.24697065353393</v>
+        <v>264.939270878771</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>361.740233281005</v>
+        <v>2.30648851394653</v>
       </c>
       <c r="B124" t="n">
-        <v>2.24710440635681</v>
+        <v>278.883451930698</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>375.894172157975</v>
+        <v>2.30778622627258</v>
       </c>
       <c r="B125" t="n">
-        <v>2.24750518798828</v>
+        <v>292.827708673917</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>389.58447579569</v>
+        <v>2.30889320373535</v>
       </c>
       <c r="B126" t="n">
-        <v>2.24784874916076</v>
+        <v>306.771962353789</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>403.738129760056</v>
+        <v>2.31137442588806</v>
       </c>
       <c r="B127" t="n">
-        <v>2.24823069572448</v>
+        <v>320.716128749253</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>417.429109952928</v>
+        <v>2.31059193611145</v>
       </c>
       <c r="B128" t="n">
-        <v>2.24849772453308</v>
+        <v>334.660292179933</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>431.582983517064</v>
+        <v>2.3120424747467</v>
       </c>
       <c r="B129" t="n">
-        <v>2.24857425689697</v>
+        <v>348.604398554797</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>445.274131025485</v>
+        <v>2.31286311149597</v>
       </c>
       <c r="B130" t="n">
-        <v>2.24905133247375</v>
+        <v>362.548508425566</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>459.427966718682</v>
+        <v>2.31559252738952</v>
       </c>
       <c r="B131" t="n">
-        <v>2.24914693832397</v>
+        <v>376.492649172734</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>473.11881997051</v>
+        <v>2.31671857833862</v>
       </c>
       <c r="B132" t="n">
-        <v>2.24947142601013</v>
+        <v>390.436684628543</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>487.272961725697</v>
+        <v>2.3177683353424</v>
       </c>
       <c r="B133" t="n">
-        <v>2.24981498718261</v>
+        <v>404.380834319045</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>500.963737446258</v>
+        <v>2.31769180297851</v>
       </c>
       <c r="B134" t="n">
-        <v>2.24991035461425</v>
+        <v>418.324928574609</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>515.117293489247</v>
+        <v>2.32019209861755</v>
       </c>
       <c r="B135" t="n">
-        <v>2.25012040138244</v>
+        <v>432.269059146593</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>528.8077797342301</v>
+        <v>2.32137537002563</v>
       </c>
       <c r="B136" t="n">
-        <v>2.25027322769165</v>
+        <v>446.213268134704</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>542.9616392205349</v>
+        <v>2.32238698005676</v>
       </c>
       <c r="B137" t="n">
-        <v>2.25054049491882</v>
+        <v>460.157411657084</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>556.65236173343</v>
+        <v>2.32290244102478</v>
       </c>
       <c r="B138" t="n">
-        <v>2.25078868865966</v>
+        <v>474.101575674925</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>570.805837176617</v>
+        <v>2.32479190826416</v>
       </c>
       <c r="B139" t="n">
-        <v>2.25099849700927</v>
+        <v>488.045751856156</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>584.496445892461</v>
+        <v>2.32605147361755</v>
       </c>
       <c r="B140" t="n">
-        <v>2.25111317634582</v>
+        <v>501.989910234195</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>598.649872991097</v>
+        <v>2.32700586318969</v>
       </c>
       <c r="B141" t="n">
-        <v>2.25113224983215</v>
+        <v>515.93409729962</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>612.340981503687</v>
+        <v>2.32775020599365</v>
       </c>
       <c r="B142" t="n">
-        <v>2.2513039112091</v>
+        <v>529.878259629695</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>626.493729571117</v>
+        <v>2.33028864860534</v>
       </c>
       <c r="B143" t="n">
-        <v>2.25134229660034</v>
+        <v>543.822342184553</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>640.184209759975</v>
+        <v>2.33023142814636</v>
       </c>
       <c r="B144" t="n">
-        <v>2.25143766403198</v>
+        <v>557.76650689722</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>654.337713725591</v>
+        <v>2.33122372627258</v>
       </c>
       <c r="B145" t="n">
-        <v>2.25149488449096</v>
+        <v>571.710608342157</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>668.027956975826</v>
+        <v>2.33152914047241</v>
       </c>
       <c r="B146" t="n">
-        <v>2.25166678428649</v>
+        <v>585.654829238297</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>682.181163319059</v>
+        <v>2.33425855636596</v>
       </c>
       <c r="B147" t="n">
-        <v>2.25172400474548</v>
+        <v>599.598994500896</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>695.871612199016</v>
+        <v>2.3353271484375</v>
       </c>
       <c r="B148" t="n">
-        <v>2.2518765926361</v>
+        <v>613.543210805281</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>710.025445366841</v>
+        <v>2.33605241775512</v>
       </c>
       <c r="B149" t="n">
-        <v>2.2518765926361</v>
+        <v>627.487379384405</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>723.716917475433</v>
+        <v>2.33683514595031</v>
       </c>
       <c r="B150" t="n">
-        <v>2.25218224525451</v>
+        <v>641.431634174174</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>737.8705755740619</v>
+        <v>2.33969783782959</v>
       </c>
       <c r="B151" t="n">
-        <v>2.2521629333496</v>
+        <v>655.375843814673</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>751.561492974356</v>
+        <v>2.34061408042907</v>
       </c>
       <c r="B152" t="n">
-        <v>2.25233483314514</v>
+        <v>669.320069833931</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>765.714655451803</v>
+        <v>2.3416256904602</v>
       </c>
       <c r="B153" t="n">
-        <v>2.25243020057678</v>
+        <v>683.2643040331531</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>779.4051500484831</v>
+        <v>2.34227442741394</v>
       </c>
       <c r="B154" t="n">
-        <v>2.25258302688598</v>
+        <v>697.208555007106</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>793.559203197566</v>
+        <v>2.34586262702941</v>
       </c>
       <c r="B155" t="n">
-        <v>2.25271654129028</v>
+        <v>711.152805008596</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>807.250376217171</v>
+        <v>2.34754228591918</v>
       </c>
       <c r="B156" t="n">
-        <v>2.2528121471405</v>
+        <v>725.097096208325</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>821.404604975185</v>
+        <v>2.34905004501342</v>
       </c>
       <c r="B157" t="n">
-        <v>2.25298380851745</v>
+        <v>739.04157151687</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>835.095389943521</v>
+        <v>2.35048151016235</v>
       </c>
       <c r="B158" t="n">
-        <v>2.25330853462219</v>
+        <v>752.985976964268</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>849.248502697951</v>
+        <v>2.35366868972778</v>
       </c>
       <c r="B159" t="n">
-        <v>2.25319385528564</v>
+        <v>766.930275697011</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>862.939014469887</v>
+        <v>2.35523390769958</v>
       </c>
       <c r="B160" t="n">
-        <v>2.25342297554016</v>
+        <v>780.8746026322769</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>877.092847332724</v>
+        <v>2.35624527931213</v>
       </c>
       <c r="B161" t="n">
-        <v>2.2532320022583</v>
+        <v>794.81893668793</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>890.783427067217</v>
+        <v>2.3582112789154</v>
       </c>
       <c r="B162" t="n">
-        <v>2.25334668159484</v>
+        <v>808.763275901871</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>904.936208523963</v>
+        <v>2.36178016662597</v>
       </c>
       <c r="B163" t="n">
-        <v>2.25344204902648</v>
+        <v>822.707550140426</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>918.6273966822901</v>
+        <v>2.36313533782959</v>
       </c>
       <c r="B164" t="n">
-        <v>2.25346112251281</v>
+        <v>836.651879226766</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>932.781160605777</v>
+        <v>2.3656165599823</v>
       </c>
       <c r="B165" t="n">
-        <v>2.25359487533569</v>
+        <v>850.596199557021</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>946.471953605057</v>
+        <v>2.36805963516235</v>
       </c>
       <c r="B166" t="n">
-        <v>2.25363302230835</v>
+        <v>864.540512328017</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>960.625039426566</v>
+        <v>2.37174320220947</v>
       </c>
       <c r="B167" t="n">
-        <v>2.25361394882202</v>
+        <v>878.484797789078</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>974.316255625532</v>
+        <v>2.37368988990783</v>
       </c>
       <c r="B168" t="n">
-        <v>2.25388121604919</v>
+        <v>892.429081188752</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>988.469076682482</v>
+        <v>2.3762092590332</v>
       </c>
       <c r="B169" t="n">
-        <v>2.25407195091247</v>
+        <v>906.373391381999</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>1002.1590998056</v>
+        <v>2.37911033630371</v>
       </c>
       <c r="B170" t="n">
-        <v>2.25451111793518</v>
+        <v>920.317744860686</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>1016.31213354222</v>
+        <v>2.38313746452331</v>
       </c>
       <c r="B171" t="n">
-        <v>2.25491189956665</v>
+        <v>934.262093676478</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>1030.00280950821</v>
+        <v>2.38638186454772</v>
       </c>
       <c r="B172" t="n">
-        <v>2.25540828704834</v>
+        <v>948.206447405976</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>1044.15641308151</v>
+        <v>2.38939762115478</v>
       </c>
       <c r="B173" t="n">
-        <v>2.25596189498901</v>
+        <v>962.150727478007</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>1057.84668150486</v>
+        <v>2.39226055145263</v>
       </c>
       <c r="B174" t="n">
-        <v>2.25670647621154</v>
+        <v>976.095067132328</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1071.99962530536</v>
+        <v>2.39584851264953</v>
       </c>
       <c r="B175" t="n">
-        <v>2.25735545158386</v>
+        <v>990.039393942372</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>1085.69019647752</v>
+        <v>2.39871144294738</v>
       </c>
       <c r="B176" t="n">
-        <v>2.25838637351989</v>
+        <v>1003.98371809137</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1099.84379577065</v>
+        <v>2.40180325508117</v>
       </c>
       <c r="B177" t="n">
-        <v>2.25958895683288</v>
+        <v>1017.92804270058</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>1113.53374774953</v>
+        <v>2.40485715866088</v>
       </c>
       <c r="B178" t="n">
-        <v>2.26105880737304</v>
+        <v>1031.87237265077</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>1127.68704456291</v>
+        <v>2.40890336036682</v>
       </c>
       <c r="B179" t="n">
-        <v>2.26268148422241</v>
+        <v>1045.81669749031</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>1141.37769835837</v>
+        <v>2.41230058670043</v>
       </c>
       <c r="B180" t="n">
-        <v>2.26499128341674</v>
+        <v>1059.76098192155</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>1155.53111274192</v>
+        <v>2.41627049446106</v>
       </c>
       <c r="B181" t="n">
-        <v>2.2683892250061</v>
+        <v>1073.70529640869</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1169.22225272179</v>
+        <v>2.42142367362976</v>
       </c>
       <c r="B182" t="n">
-        <v>2.27325701713562</v>
+        <v>1087.64957230405</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1183.3754769465</v>
+        <v>2.42978334426879</v>
       </c>
       <c r="B183" t="n">
-        <v>2.28152298927307</v>
+        <v>1101.59386755225</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1197.0655187501</v>
+        <v>2.44140648841857</v>
       </c>
       <c r="B184" t="n">
-        <v>2.2969856262207</v>
+        <v>1115.53810881073</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1206.86998397241</v>
+        <v>2.47933030128479</v>
       </c>
       <c r="B185" t="n">
-        <v>2.3160560131073</v>
+        <v>1129.48232230235</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1212.00864768579</v>
+        <v>2.59323477745056</v>
       </c>
       <c r="B186" t="n">
-        <v>2.33216786384582</v>
+        <v>1143.42658642526</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1215.95349915548</v>
+        <v>2.69782543182373</v>
       </c>
       <c r="B187" t="n">
-        <v>2.34669494628906</v>
+        <v>1157.37085255023</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1219.59899659911</v>
+        <v>2.73737120628356</v>
       </c>
       <c r="B188" t="n">
-        <v>2.35931324958801</v>
+        <v>1171.31507023907</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1222.49965949914</v>
+        <v>2.76256465911865</v>
       </c>
       <c r="B189" t="n">
-        <v>2.36862897872924</v>
+        <v>1185.25924796691</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>2.78207039833068</v>
+      </c>
+      <c r="B190" t="n">
+        <v>1199.20350956869</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>2.80735921859741</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1213.14781338938</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>2.8223226070404</v>
+      </c>
+      <c r="B192" t="n">
+        <v>1227.09209712175</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>2.83659887313842</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1241.03635868952</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>2.84709596633911</v>
+      </c>
+      <c r="B194" t="n">
+        <v>1254.98061214218</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>2.87028527259826</v>
+      </c>
+      <c r="B195" t="n">
+        <v>1268.92480634692</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>2.88467621803283</v>
+      </c>
+      <c r="B196" t="n">
+        <v>1282.86905473802</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>2.90145254135131</v>
+      </c>
+      <c r="B197" t="n">
+        <v>1296.81334563021</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>2.91939330101013</v>
+      </c>
+      <c r="B198" t="n">
+        <v>1310.75760094126</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>2.94195294380188</v>
+      </c>
+      <c r="B199" t="n">
+        <v>1324.70188284414</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>2.95787048339843</v>
+      </c>
+      <c r="B200" t="n">
+        <v>1338.64613894658</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>2.97300553321838</v>
+      </c>
+      <c r="B201" t="n">
+        <v>1352.59032129336</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2.98731994628906</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1365.44937912671</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>3.00003123283386</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1376.11207001509</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2.9948399066925</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1385.1880859789</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2.99982118606567</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1393.43891118104</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2.99541234970092</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1400.98261810903</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>3.00001215934753</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1408.04615696087</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>3.00006937980651</v>
+      </c>
+      <c r="B208" t="n">
+        <v>1414.59422913876</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2.99079370498657</v>
+      </c>
+      <c r="B209" t="n">
+        <v>1420.71921385594</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2.98836970329284</v>
+      </c>
+      <c r="B210" t="n">
+        <v>1426.54211063111</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2.99640488624572</v>
+      </c>
+      <c r="B211" t="n">
+        <v>1431.97477437747</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2.98554491996765</v>
+      </c>
+      <c r="B212" t="n">
+        <v>1437.09851859442</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2.98718643188476</v>
+      </c>
+      <c r="B213" t="n">
+        <v>1441.96035002498</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2.99642395973205</v>
+      </c>
+      <c r="B214" t="n">
+        <v>1446.59023887122</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2.98176598548889</v>
+      </c>
+      <c r="B215" t="n">
+        <v>1451.00951834007</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2.9741506576538</v>
+      </c>
+      <c r="B216" t="n">
+        <v>1455.23413104378</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2.97105884552002</v>
+      </c>
+      <c r="B217" t="n">
+        <v>1459.32720630489</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2.97716617584228</v>
+      </c>
+      <c r="B218" t="n">
+        <v>1463.29092571976</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2.98850321769714</v>
+      </c>
+      <c r="B219" t="n">
+        <v>1467.08512459904</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2.95966458320617</v>
+      </c>
+      <c r="B220" t="n">
+        <v>1470.75609479327</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2.99064087867736</v>
+      </c>
+      <c r="B221" t="n">
+        <v>1474.27857991003</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2.97949481010437</v>
+      </c>
+      <c r="B222" t="n">
+        <v>1477.67434070722</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2.97247123718261</v>
+      </c>
+      <c r="B223" t="n">
+        <v>1480.9213346283</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2.97355914115905</v>
+      </c>
+      <c r="B224" t="n">
+        <v>1484.04520101303</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2.98718643188476</v>
+      </c>
+      <c r="B225" t="n">
+        <v>1487.10534423987</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>3.00010752677917</v>
+      </c>
+      <c r="B226" t="n">
+        <v>1490.05492174277</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2.96794772148132</v>
+      </c>
+      <c r="B227" t="n">
+        <v>1492.88923843859</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2.99713015556335</v>
+      </c>
+      <c r="B228" t="n">
+        <v>1495.62010930164</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2.97327280044555</v>
+      </c>
+      <c r="B229" t="n">
+        <v>1498.28724902434</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2.9532516002655</v>
+      </c>
+      <c r="B230" t="n">
+        <v>1500.85096041106</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>3.00001215934753</v>
+      </c>
+      <c r="B231" t="n">
+        <v>1503.33869935895</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2.99678659439086</v>
+      </c>
+      <c r="B232" t="n">
+        <v>1505.74990525718</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2.99382829666137</v>
+      </c>
+      <c r="B233" t="n">
+        <v>1508.0879305595</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2.99915313720703</v>
+      </c>
+      <c r="B234" t="n">
+        <v>1510.33157214938</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>3.00018382072448</v>
+      </c>
+      <c r="B235" t="n">
+        <v>1512.49891984659</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2.95017886161804</v>
+      </c>
+      <c r="B236" t="n">
+        <v>1514.57297724368</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2.97441792488098</v>
+      </c>
+      <c r="B237" t="n">
+        <v>1516.56895970728</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2.99993562698364</v>
+      </c>
+      <c r="B238" t="n">
+        <v>1518.46191289888</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2.96934103965759</v>
+      </c>
+      <c r="B239" t="n">
+        <v>1520.27707110737</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2.9368188381195</v>
+      </c>
+      <c r="B240" t="n">
+        <v>1522.01600487448</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2.990736246109</v>
+      </c>
+      <c r="B241" t="n">
+        <v>1523.68003607078</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2.97705173492431</v>
+      </c>
+      <c r="B242" t="n">
+        <v>1525.27128663177</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2.96292829513549</v>
+      </c>
+      <c r="B243" t="n">
+        <v>1526.77475790627</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2.95989346504211</v>
+      </c>
+      <c r="B244" t="n">
+        <v>1528.20288761743</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2.96603918075561</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1529.55755687024</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2.9721086025238</v>
+      </c>
+      <c r="B246" t="n">
+        <v>1530.84086289505</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2.98878955841064</v>
+      </c>
+      <c r="B247" t="n">
+        <v>1532.04232081643</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>3.00008845329284</v>
+      </c>
+      <c r="B248" t="n">
+        <v>1533.17916581696</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2.94765949249267</v>
+      </c>
+      <c r="B249" t="n">
+        <v>1534.25224117422</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2.98634648323059</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1535.27143199618</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2.93584537506103</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1536.24680268275</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2.98441886901855</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1537.18800776408</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2.94258260726928</v>
+      </c>
+      <c r="B253" t="n">
+        <v>1538.08900273956</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2.99138522148132</v>
+      </c>
+      <c r="B254" t="n">
+        <v>1538.96532881398</v>
       </c>
     </row>
   </sheetData>
